--- a/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18900" yWindow="-20420" windowWidth="30240" windowHeight="17300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chess Clock" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemini Generation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chess Clock" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C1" s="12" t="inlineStr">
         <is>
-          <t>GPT-5 Generation</t>
+          <t>Grading</t>
         </is>
       </c>
       <c r="D1" s="12" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>Represented by [*] --&gt; Off at the top level</t>
+          <t>Initial state pointing to Off is present</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>Transition [*] --&gt; Off is present</t>
+          <t>Transition from initial state to Off is present</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Off state is explicitly defined</t>
+          <t>Off state is present</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Off --&gt; On : onOff / powerOn() transition is present</t>
+          <t>Transition from Off to On is present</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>On composite state is defined with nested states</t>
+          <t>On is a composite state</t>
         </is>
       </c>
     </row>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>[*] --&gt; Setup within On state serves as initial state</t>
+          <t>Initial state inside On is present</t>
         </is>
       </c>
     </row>
@@ -6015,11 +6015,11 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Represented by Setup composite state which handles timing selection and orientation</t>
+          <t>Setup state exists as Configuring but is not composite</t>
         </is>
       </c>
     </row>
@@ -6035,11 +6035,11 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>ChoosingTiming handles timing selection functionality as a region-equivalent structure</t>
+          <t>No parallel regions used in setup</t>
         </is>
       </c>
     </row>
@@ -6055,11 +6055,11 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>[*] --&gt; ChoosingTiming serves as initial state for timing selection</t>
+          <t>No region 1 present</t>
         </is>
       </c>
     </row>
@@ -6075,11 +6075,11 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>ChoosingTiming with BrowseWhiteLeft and BrowseWhiteRight represents timing selection</t>
+          <t>Handled within Configuring state</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>showNextPredefinedTiming() action on plus button captures increment behavior</t>
+          <t>Action nextTiming() is present</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>showPreviousPredefinedTiming() action on minus button captures decrement behavior</t>
+          <t>Action prevTiming() is present</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Self-transitions on BrowseWhiteLeft and BrowseWhiteRight with plus/minus events</t>
+          <t>Self-transitions for timing selection are present</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>BrowseWhiteLeft/Right --&gt; ReadyWhiteLeft/Right : select transitions present</t>
+          <t>Transition to ReadyToStart is present</t>
         </is>
       </c>
     </row>
@@ -6175,11 +6175,11 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>TimingSelected with ReadyWhiteLeft and ReadyWhiteRight handles orientation as region-equivalent</t>
+          <t>No parallel regions used</t>
         </is>
       </c>
     </row>
@@ -6195,11 +6195,11 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>[*] --&gt; ReadyWhiteLeft in TimingSelected serves as initial state</t>
+          <t>No region 2 present</t>
         </is>
       </c>
       <c r="E17" s="7" t="n"/>
@@ -6233,11 +6233,11 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>BrowseWhiteLeft and ReadyWhiteLeft represent white king on left orientation</t>
+          <t>Not explicitly modeled as a state</t>
         </is>
       </c>
     </row>
@@ -6253,11 +6253,11 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>BrowseWhiteRight and ReadyWhiteRight represent white king on right orientation</t>
+          <t>Not explicitly modeled as a state</t>
         </is>
       </c>
     </row>
@@ -6273,11 +6273,11 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>[*] --&gt; BrowseWhiteLeft serves as initial transition to white king on left</t>
+          <t>Not modeled</t>
         </is>
       </c>
     </row>
@@ -6293,11 +6293,11 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>flip transitions between BrowseWhiteLeft and BrowseWhiteRight and between ReadyWhiteLeft and ReadyWhiteRight</t>
+          <t>Modeled as a self-transition with swapColors action</t>
         </is>
       </c>
     </row>
@@ -6313,11 +6313,11 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>flip transitions in reverse direction are present</t>
+          <t>Modeled as a self-transition with swapColors action</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>TimingSelected state with ReadyWhiteLeft and ReadyWhiteRight represents ready to start</t>
+          <t>ReadyToStart state is present</t>
         </is>
       </c>
       <c r="E23" s="7" t="n"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>ReadyWhiteLeft/Right --&gt; Game : startStop transitions present</t>
+          <t>Transition to ActiveGame is present</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>GameRunning composite state is defined with clock states</t>
+          <t>ActiveGame is a composite state</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>H history state is defined within GameRunning</t>
+          <t>History state H is present</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>WhiteRunning state is present</t>
+          <t>WhiteTurn state is present</t>
         </is>
       </c>
     </row>
@@ -6451,11 +6451,11 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>startWhiteCountdown() entry action captures starting white timer</t>
+          <t>No explicit startTimer action; timer modeled via after1sec transitions</t>
         </is>
       </c>
     </row>
@@ -6471,11 +6471,11 @@
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>stopWhiteCountdown() exit action captures stopping white timer</t>
+          <t>No explicit stopTimer action</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>[whiteTime &gt; 1] guard on self-transition captures clock running condition</t>
+          <t>Guard whiteTime &gt; 0 is present</t>
         </is>
       </c>
       <c r="E30" s="7" t="n"/>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>decrementWhiteClock() action captures decrementing white clock</t>
+          <t>Action decrementWhite() is present</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>WhiteRunning --&gt; WhiteRunning self-transition with after1sec event</t>
+          <t>Self-transition for white clock is present</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>BlackRunning state is present</t>
+          <t>BlackTurn state is present</t>
         </is>
       </c>
     </row>
@@ -6607,11 +6607,11 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>startBlackCountdown() entry action captures starting black timer</t>
+          <t>No explicit startTimer action; timer modeled via after1sec transitions</t>
         </is>
       </c>
     </row>
@@ -6627,11 +6627,11 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>stopBlackCountdown() exit action captures stopping black timer</t>
+          <t>No explicit stopTimer action</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>[blackTime &gt; 1] guard on self-transition captures clock running condition</t>
+          <t>Guard blackTime &gt; 0 is present</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>decrementBlackClock() action captures decrementing black clock</t>
+          <t>Action decrementBlack() is present</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>BlackRunning --&gt; BlackRunning self-transition with after1sec event</t>
+          <t>Self-transition for black clock is present</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>GameRunning --&gt; Paused : startStop transition is present</t>
+          <t>Transition to Paused is present</t>
         </is>
       </c>
       <c r="E39" s="7" t="n"/>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>WhiteRunning --&gt; WhiteFlag and BlackRunning --&gt; BlackFlag transitions represent game finishing</t>
+          <t>Transitions to Flagged state are present</t>
         </is>
       </c>
       <c r="E40" s="7" t="n"/>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>[whiteTime &lt;= 1] guard on transition to WhiteFlag captures zero condition</t>
+          <t>Guard whiteTime == 0 is present</t>
         </is>
       </c>
       <c r="E41" s="7" t="n"/>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>[blackTime &lt;= 1] guard on transition to BlackFlag captures zero condition</t>
+          <t>Guard blackTime == 0 is present</t>
         </is>
       </c>
       <c r="E42" s="7" t="n"/>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>Paused state is present within Game composite state</t>
+          <t>Paused state is present</t>
         </is>
       </c>
       <c r="E43" s="7" t="n"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Paused --&gt; H : startStop transition resumes game</t>
+          <t>Transition from Paused to History state is present</t>
         </is>
       </c>
       <c r="E44" s="7" t="n"/>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>WhiteFlag and BlackFlag states represent game finished conditions</t>
+          <t>Flagged state is present</t>
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>On --&gt; Off : onOff / powerOff() transition is present</t>
+          <t>Transition from On to Off is present</t>
         </is>
       </c>
       <c r="E46" s="7" t="n"/>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect states present</t>
+          <t>No fundamentally incorrect additional states</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>All transitions are reasonable and support the system behavior</t>
+          <t>Extra transitions are reasonable modeling choices</t>
         </is>
       </c>
       <c r="E48" s="7" t="n"/>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>All guards are appropriate for the modeled behavior</t>
+          <t>No incorrect additional guards</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>All actions are reasonable and support the system requirements</t>
+          <t>Additional actions correctly model the increment logic</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>Game composite state is a reasonable organizational choice</t>
+          <t>No incorrect additional composite states</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>No incorrect regions present</t>
+          <t>No incorrect additional regions</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>History state usage is appropriate</t>
+          <t>No incorrect additional history states</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
     <row r="1" ht="15.75" customHeight="1" s="68">
       <c r="A1" s="67" t="inlineStr">
         <is>
-          <t>Generated by GPT-5</t>
+          <t>Generated by Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="J1" s="23" t="inlineStr">
@@ -11043,15 +11043,15 @@
         <v/>
       </c>
       <c r="C3" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$46, $A3, 'GPT-5 Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D3" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$47:$A$53, $A3, 'GPT-5 Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A3, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E3" s="28">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$46, $A3, 'GPT-5 Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F3" s="28">
@@ -11080,15 +11080,15 @@
         <v/>
       </c>
       <c r="C4" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$46, $A4, 'GPT-5 Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D4" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$47:$A$53, $A4, 'GPT-5 Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A4, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E4" s="28">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$46, $A4, 'GPT-5 Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F4" s="28">
@@ -11121,15 +11121,15 @@
         <v/>
       </c>
       <c r="C5" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$46, $A5, 'GPT-5 Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D5" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$47:$A$53, $A5, 'GPT-5 Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A5, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E5" s="28">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$46, $A5, 'GPT-5 Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F5" s="28">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="J5" s="25" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="K5" s="15" t="n"/>
@@ -11162,15 +11162,15 @@
         <v/>
       </c>
       <c r="C6" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$46, $A6, 'GPT-5 Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D6" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$47:$A$53, $A6, 'GPT-5 Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A6, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E6" s="28">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$46, $A6, 'GPT-5 Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F6" s="28">
@@ -11199,15 +11199,15 @@
         <v/>
       </c>
       <c r="C7" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$46, $A7, 'GPT-5 Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D7" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$47:$A$53, $A7, 'GPT-5 Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A7, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E7" s="28">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$46, $A7, 'GPT-5 Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F7" s="28">
@@ -11239,15 +11239,15 @@
         <v/>
       </c>
       <c r="C8" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$46, $A8, 'GPT-5 Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D8" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$47:$A$53, $A8, 'GPT-5 Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A8, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$46, $A8, 'GPT-5 Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F8" s="28">
@@ -11264,7 +11264,7 @@
       </c>
       <c r="J8" s="65" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -11279,15 +11279,15 @@
         <v/>
       </c>
       <c r="C9" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$46, $A9, 'GPT-5 Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>SUMIF('GPT-5 Generation'!$A$47:$A$53, $A9, 'GPT-5 Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A9, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$46, $A9, 'GPT-5 Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F9" s="28">

--- a/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Chess Clock" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gemini 3.1 Pro Grading" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -11043,15 +11043,15 @@
         <v/>
       </c>
       <c r="C3" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D3" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A3, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$47:$A$53, $A3, 'Gemini 3.1 Pro Grading'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E3" s="28">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F3" s="28">
@@ -11080,15 +11080,15 @@
         <v/>
       </c>
       <c r="C4" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D4" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A4, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$47:$A$53, $A4, 'Gemini 3.1 Pro Grading'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E4" s="28">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F4" s="28">
@@ -11121,15 +11121,15 @@
         <v/>
       </c>
       <c r="C5" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D5" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A5, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$47:$A$53, $A5, 'Gemini 3.1 Pro Grading'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E5" s="28">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F5" s="28">
@@ -11162,15 +11162,15 @@
         <v/>
       </c>
       <c r="C6" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D6" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A6, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$47:$A$53, $A6, 'Gemini 3.1 Pro Grading'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E6" s="28">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F6" s="28">
@@ -11199,15 +11199,15 @@
         <v/>
       </c>
       <c r="C7" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D7" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A7, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$47:$A$53, $A7, 'Gemini 3.1 Pro Grading'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E7" s="28">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F7" s="28">
@@ -11239,15 +11239,15 @@
         <v/>
       </c>
       <c r="C8" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D8" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A8, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$47:$A$53, $A8, 'Gemini 3.1 Pro Grading'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F8" s="28">
@@ -11279,15 +11279,15 @@
         <v/>
       </c>
       <c r="C9" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$46)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$46)</f>
         <v/>
       </c>
       <c r="D9" s="28">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$47:$A$53, $A9, 'Gemini 3.1 Pro Generation'!$C$47:$C$53)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$47:$A$53, $A9, 'Gemini 3.1 Pro Grading'!$C$47:$C$53)</f>
         <v/>
       </c>
       <c r="E9" s="28">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$46, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$46,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$46, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$46,0)</f>
         <v/>
       </c>
       <c r="F9" s="28">
